--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-03.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-03.xlsx
@@ -474,37 +474,37 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583991830941</v>
+        <v>5583999412481</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Joao Lucas Justino de Araujo</t>
+          <t>Marcos Leao dos Santos Farias</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5581998601254</v>
+        <v>5583987954004</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ademilton</t>
+          <t>Aglai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ademilton Fernandes da Silva</t>
+          <t>Aglai de Araujo Alves</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583996309806</v>
+        <v>5583991830941</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -513,712 +513,712 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Joao Paulo Cruz de Oliveira</t>
+          <t>Joao Lucas Justino de Araujo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987898940</v>
+        <v>5581998601254</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Ademilton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Francisco Araujo</t>
+          <t>Ademilton Fernandes da Silva</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5513997089777</v>
+        <v>5583996309806</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alexandre Gallo</t>
+          <t>Joao Paulo Cruz de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583981845987</v>
+        <v>5583987898940</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marivone</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marivone Cavalcante da Silva Duarte</t>
+          <t>Francisco Araujo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583991093434</v>
+        <v>5513997089777</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>David Pereira Ferreira</t>
+          <t>Alexandre Gallo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583986148350</v>
+        <v>5583981845987</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Marivone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luiz Carlos Guedes Frazao</t>
+          <t>Marivone Cavalcante da Silva Duarte</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583988546320</v>
+        <v>5583991093434</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patricia Assis Duarte</t>
+          <t>David Pereira Ferreira</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583994196122</v>
+        <v>5583986148350</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alessandro</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alessandro Costa do Nascimento</t>
+          <t>Luiz Carlos Guedes Frazao</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583998036581</v>
+        <v>5583988546320</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marcelo Martins Franca</t>
+          <t>Patricia Assis Duarte</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583987107201</v>
+        <v>5583994196122</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nery</t>
+          <t>Alessandro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nery Delfino da Silva</t>
+          <t>Alessandro Costa do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5584994969956</v>
+        <v>5583998036581</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Funpec</t>
+          <t>Marcelo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Funpec</t>
+          <t>Marcelo Martins Franca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583987787611</v>
+        <v>5583987107201</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luzinete</t>
+          <t>Nery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luzinete Fatima de Souza Sales</t>
+          <t>Nery Delfino da Silva</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988906107</v>
+        <v>5584994969956</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Funpec</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sandra Nivea Alves Grigorio</t>
+          <t>Funpec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583996572156</v>
+        <v>5583987787611</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Luzinete</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fabio Dutra de Melo</t>
+          <t>Luzinete Fatima de Souza Sales</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583998314991</v>
+        <v>5583988906107</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Antares</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Antares Infraestrutura</t>
+          <t>Sandra Nivea Alves Grigorio</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583999066267</v>
+        <v>5583996572156</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Claudilane</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Claudilane dos Santos Silva</t>
+          <t>Fabio Dutra de Melo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583999544755</v>
+        <v>5583998314991</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luciane</t>
+          <t>Antares</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luciane Silva de Oliveira</t>
+          <t>Antares Infraestrutura</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988332840</v>
+        <v>5583999066267</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Claudilane</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>David Ferreira do Nascimento</t>
+          <t>Claudilane dos Santos Silva</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583988013545</v>
+        <v>5583999544755</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Graciane</t>
+          <t>Luciane</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Graciane Coutinho</t>
+          <t>Luciane Silva de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583986814093</v>
+        <v>5583988332840</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Olidia</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Olidia Maria Cantalice de Oliveira</t>
+          <t>David Ferreira do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583988693422</v>
+        <v>5583988013545</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Girlene</t>
+          <t>Graciane</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Girlene Maria Lima dos Santos</t>
+          <t>Graciane Coutinho</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583986871608</v>
+        <v>5583986814093</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heider</t>
+          <t>Olidia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Heider Araujo</t>
+          <t>Olidia Maria Cantalice de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583987616091</v>
+        <v>5583988693422</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Claudete</t>
+          <t>Girlene</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Claudete da Fonseca</t>
+          <t>Girlene Maria Lima dos Santos</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583982281037</v>
+        <v>5583986871608</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Heider</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fabio Vieira Soares da Silva</t>
+          <t>Heider Araujo</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583991774151</v>
+        <v>5583987616091</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adiel</t>
+          <t>Claudete</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adiel da Cruz Silva</t>
+          <t>Claudete da Fonseca</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583988209305</v>
+        <v>5583982281037</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alan Henrique Correia</t>
+          <t>Fabio Vieira Soares da Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583998591731</v>
+        <v>5583991774151</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Adiel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leandro Andre da Silva</t>
+          <t>Adiel da Cruz Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583988102759</v>
+        <v>5583988209305</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carlos Ivan dos Santos Gomes</t>
+          <t>Alan Henrique Correia</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583999157763</v>
+        <v>5583998591731</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maria Napolitana Leite Andrelino</t>
+          <t>Leandro Andre da Silva</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583987603968</v>
+        <v>5583988102759</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ronielle</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ronielle Abrandes Silva</t>
+          <t>Carlos Ivan dos Santos Gomes</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583988065813</v>
+        <v>5583999157763</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jose Ricardo Lima da Silva</t>
+          <t>Maria Napolitana Leite Andrelino</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5584988968882</v>
+        <v>5583987603968</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Terca</t>
+          <t>Ronielle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Terca da Serra</t>
+          <t>Ronielle Abrandes Silva</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583996477125</v>
+        <v>5583988065813</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Daniel Luis Batista Nunes de Franca</t>
+          <t>Jose Ricardo Lima da Silva</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583987980938</v>
+        <v>5584988968882</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>Terca</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marcelo Oliveira de Lima</t>
+          <t>Terca da Serra</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583989154519</v>
+        <v>5583996477125</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wilton</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wilton Jones Souto de Sousa</t>
+          <t>Daniel Luis Batista Nunes de Franca</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583996905861</v>
+        <v>5583987980938</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Giovani</t>
+          <t>Marcelo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Giovani Luiz de Carvalho Bezerra</t>
+          <t>Marcelo Oliveira de Lima</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988477790</v>
+        <v>5583989154519</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Elivaldo</t>
+          <t>Wilton</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elivaldo Ferreira de Paiva</t>
+          <t>Wilton Jones Souto de Sousa</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583981157039</v>
+        <v>5583996905861</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Janieli</t>
+          <t>Giovani</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Janieli Alves Ferreira</t>
+          <t>Giovani Luiz de Carvalho Bezerra</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583988002307</v>
+        <v>5583988477790</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Juarez</t>
+          <t>Elivaldo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Juarez Alves</t>
+          <t>Elivaldo Ferreira de Paiva</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583991826991</v>
+        <v>5583981157039</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Damiao</t>
+          <t>Janieli</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Damiao Alves Severiano</t>
+          <t>Janieli Alves Ferreira</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583987929127</v>
+        <v>5583988002307</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Juarez</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Antonio Angelo da Costa</t>
+          <t>Juarez Alves</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988720615</v>
+        <v>5583991826991</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Damiao</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Caio Rodrigo Dantas Lucena</t>
+          <t>Damiao Alves Severiano</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5511980957712</v>
+        <v>5583987929127</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alan Vieira</t>
+          <t>Antonio Angelo da Costa</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583998591068</v>
+        <v>5583988720615</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adilson</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Adilson Mateus Araujo Ribeiro</t>
+          <t>Caio Rodrigo Dantas Lucena</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5584996664408</v>
+        <v>5511980957712</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Isabel Ruciane Silva</t>
+          <t>Alan Vieira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5581988225555</v>
+        <v>5583998591068</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Evaldo</t>
+          <t>Adilson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Evaldo Silva de Almeida</t>
+          <t>Adilson Mateus Araujo Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583987357458</v>
+        <v>5584996664408</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Michelle da Silva Nogueira</t>
+          <t>Isabel Ruciane Silva</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583986190187</v>
+        <v>5581988225555</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wictor</t>
+          <t>Evaldo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wictor Abner de Oliveira Jácome</t>
+          <t>Evaldo Silva de Almeida</t>
         </is>
       </c>
     </row>
